--- a/R Markdown/resultados/Produtos_Cesta_2026/tabelas/tabela_valores_por_subprefeitura.xlsx
+++ b/R Markdown/resultados/Produtos_Cesta_2026/tabelas/tabela_valores_por_subprefeitura.xlsx
@@ -1,176 +1,186 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/resultados/Produtos_Cesta_2026/tabelas/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_05881C1CD90F55B416BB1BBBCC2088D9147CA8D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F0EB0B8-B0ED-457C-95F7-AE6FD6BE3642}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2022" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2023" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2024" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Agregado_2022_2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2022" sheetId="1" r:id="rId1"/>
+    <sheet name="2023" sheetId="2" r:id="rId2"/>
+    <sheet name="2024" sheetId="3" r:id="rId3"/>
+    <sheet name="2025" sheetId="4" r:id="rId4"/>
+    <sheet name="Agregado_2022_2025" sheetId="5" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
-  <si>
-    <t xml:space="preserve">Subprefeitura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor_Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Categoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supra Subprefeitura Sul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dentro do IDRGP Alvo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Sé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Capela do Socorro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura M'Boi Mirim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Ipiranga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Cidade Ademar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Parelheiros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Itaquera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura de Guaianases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Butantã</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Campo Limpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Ermelino Matarazzo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Sapopemba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Perus/Anhanguera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Jabaquara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Penha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Lapa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura São Mateus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Freguesia/Brasilândia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Jaçanã/Tremembé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Mooca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Pirituba/Jaraguá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supra Subprefeitura CRS Norte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Aricanduva/Formosa/Carrão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Santo Amaro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Itaim Paulista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Casa Verde/Cachoeirinha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Vila Maria/Vila Guilherme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supra Subprefeitura Leste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Pinheiros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura São Miguel Paulista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supra Subprefeitura Centro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supra Subprefeitura Norte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura de Vila Prudente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supra Subprefeitura CRS Oeste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Vila Mariana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supra Subprefeitura CRS Sul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Cidade Tiradentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supra Subprefeitura CRS Leste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supra Subprefeitura CRS Centro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subprefeitura Santana/Tucuruvi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supra Subprefeitura CRS Sudeste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supra Subprefeitura Oeste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acima do IDRGP Alvo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abaixo do IDRGP Alvo</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="49">
+  <si>
+    <t>Subprefeitura</t>
+  </si>
+  <si>
+    <t>Valor_Total</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>Supra Subprefeitura Sul</t>
+  </si>
+  <si>
+    <t>Dentro do IDRGP Alvo</t>
+  </si>
+  <si>
+    <t>Subprefeitura Sé</t>
+  </si>
+  <si>
+    <t>Subprefeitura Capela do Socorro</t>
+  </si>
+  <si>
+    <t>Subprefeitura M'Boi Mirim</t>
+  </si>
+  <si>
+    <t>Subprefeitura Ipiranga</t>
+  </si>
+  <si>
+    <t>Subprefeitura Cidade Ademar</t>
+  </si>
+  <si>
+    <t>Subprefeitura Parelheiros</t>
+  </si>
+  <si>
+    <t>Subprefeitura Itaquera</t>
+  </si>
+  <si>
+    <t>Subprefeitura de Guaianases</t>
+  </si>
+  <si>
+    <t>Subprefeitura Butantã</t>
+  </si>
+  <si>
+    <t>Subprefeitura Campo Limpo</t>
+  </si>
+  <si>
+    <t>Subprefeitura Ermelino Matarazzo</t>
+  </si>
+  <si>
+    <t>Subprefeitura Sapopemba</t>
+  </si>
+  <si>
+    <t>Subprefeitura Perus/Anhanguera</t>
+  </si>
+  <si>
+    <t>Subprefeitura Jabaquara</t>
+  </si>
+  <si>
+    <t>Subprefeitura Penha</t>
+  </si>
+  <si>
+    <t>Subprefeitura Lapa</t>
+  </si>
+  <si>
+    <t>Subprefeitura São Mateus</t>
+  </si>
+  <si>
+    <t>Subprefeitura Freguesia/Brasilândia</t>
+  </si>
+  <si>
+    <t>Subprefeitura Jaçanã/Tremembé</t>
+  </si>
+  <si>
+    <t>Subprefeitura Mooca</t>
+  </si>
+  <si>
+    <t>Subprefeitura Pirituba/Jaraguá</t>
+  </si>
+  <si>
+    <t>Supra Subprefeitura CRS Norte</t>
+  </si>
+  <si>
+    <t>Subprefeitura Aricanduva/Formosa/Carrão</t>
+  </si>
+  <si>
+    <t>Subprefeitura Santo Amaro</t>
+  </si>
+  <si>
+    <t>Subprefeitura Itaim Paulista</t>
+  </si>
+  <si>
+    <t>Subprefeitura Casa Verde/Cachoeirinha</t>
+  </si>
+  <si>
+    <t>Subprefeitura Vila Maria/Vila Guilherme</t>
+  </si>
+  <si>
+    <t>Supra Subprefeitura Leste</t>
+  </si>
+  <si>
+    <t>Subprefeitura Pinheiros</t>
+  </si>
+  <si>
+    <t>Subprefeitura São Miguel Paulista</t>
+  </si>
+  <si>
+    <t>Supra Subprefeitura Centro</t>
+  </si>
+  <si>
+    <t>Supra Subprefeitura Norte</t>
+  </si>
+  <si>
+    <t>Subprefeitura de Vila Prudente</t>
+  </si>
+  <si>
+    <t>Supra Subprefeitura CRS Oeste</t>
+  </si>
+  <si>
+    <t>Subprefeitura Vila Mariana</t>
+  </si>
+  <si>
+    <t>Supra Subprefeitura CRS Sul</t>
+  </si>
+  <si>
+    <t>Subprefeitura Cidade Tiradentes</t>
+  </si>
+  <si>
+    <t>Supra Subprefeitura CRS Leste</t>
+  </si>
+  <si>
+    <t>Supra Subprefeitura CRS Centro</t>
+  </si>
+  <si>
+    <t>Subprefeitura Santana/Tucuruvi</t>
+  </si>
+  <si>
+    <t>Supra Subprefeitura CRS Sudeste</t>
+  </si>
+  <si>
+    <t>Supra Subprefeitura Oeste</t>
+  </si>
+  <si>
+    <t>Acima do IDRGP Alvo</t>
+  </si>
+  <si>
+    <t>Abaixo do IDRGP Alvo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -179,10 +189,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -207,19 +224,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -501,16 +530,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C44"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,474 +550,474 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="n">
-        <v>544497715.04</v>
+      <c r="B2">
+        <v>544497715.03999996</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>260246375.81</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>227299222</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>214795955</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>169838358.16</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>156055369.81</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>136627157.72</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>112845897.37</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>100139503.72</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" t="n">
-        <v>91954753.65</v>
+      <c r="B11">
+        <v>91954753.650000006</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="n">
-        <v>84428664.79</v>
+      <c r="B12">
+        <v>84428664.790000007</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
-      <c r="B13" t="n">
-        <v>79958838.31</v>
+      <c r="B13">
+        <v>79958838.310000002</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
-      <c r="B14" t="n">
-        <v>77602087.92</v>
+      <c r="B14">
+        <v>77602087.920000002</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="B15" t="n">
-        <v>59966293.89</v>
+      <c r="B15">
+        <v>59966293.890000001</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
-      <c r="B16" t="n">
-        <v>46396790.72</v>
+      <c r="B16">
+        <v>46396790.719999999</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
-      <c r="B17" t="n">
-        <v>46070835.49</v>
+      <c r="B17">
+        <v>46070835.490000002</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
-      <c r="B18" t="n">
-        <v>37890653.29</v>
+      <c r="B18">
+        <v>37890653.289999999</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
-      <c r="B19" t="n">
-        <v>35971519.64</v>
+      <c r="B19">
+        <v>35971519.640000001</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
-      <c r="B20" t="n">
-        <v>34285351.77</v>
+      <c r="B20">
+        <v>34285351.770000003</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
-      <c r="B21" t="n">
-        <v>27600079.03</v>
+      <c r="B21">
+        <v>27600079.030000001</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
-      <c r="B22" t="n">
-        <v>27343922.17</v>
+      <c r="B22">
+        <v>27343922.170000002</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
-      <c r="B23" t="n">
-        <v>26898254.97</v>
+      <c r="B23">
+        <v>26898254.969999999</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
-      <c r="B24" t="n">
-        <v>26022627.58</v>
+      <c r="B24">
+        <v>26022627.579999998</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
-      <c r="B25" t="n">
-        <v>25644053.69</v>
+      <c r="B25">
+        <v>25644053.690000001</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
-      <c r="B26" t="n">
-        <v>24864824.06</v>
+      <c r="B26">
+        <v>24864824.059999999</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
-      <c r="B27" t="n">
-        <v>24331147.69</v>
+      <c r="B27">
+        <v>24331147.690000001</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
-      <c r="B28" t="n">
-        <v>24167340.26</v>
+      <c r="B28">
+        <v>24167340.260000002</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>21750761.02</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
-      <c r="B30" t="n">
-        <v>19676217.46</v>
+      <c r="B30">
+        <v>19676217.460000001</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
-      <c r="B31" t="n">
-        <v>18620970.01</v>
+      <c r="B31">
+        <v>18620970.010000002</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>18136421.68</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
-      <c r="B33" t="n">
-        <v>17572135.83</v>
+      <c r="B33">
+        <v>17572135.829999998</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>16490084.48</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
-      <c r="B35" t="n">
-        <v>16319167.28</v>
+      <c r="B35">
+        <v>16319167.279999999</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>16310292.75</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
-      <c r="B37" t="n">
-        <v>16187870.46</v>
+      <c r="B37">
+        <v>16187870.460000001</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>14721070.74</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
-      <c r="B39" t="n">
-        <v>13597624.95</v>
+      <c r="B39">
+        <v>13597624.949999999</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
-      <c r="B40" t="n">
-        <v>9851868.14</v>
+      <c r="B40">
+        <v>9851868.1400000006</v>
       </c>
       <c r="C40" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
-      <c r="B41" t="n">
-        <v>9754879.8</v>
+      <c r="B41">
+        <v>9754879.8000000007</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
-      <c r="B42" t="n">
-        <v>8915550.77</v>
+      <c r="B42">
+        <v>8915550.7699999996</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
-      <c r="B43" t="n">
-        <v>7142999.8</v>
+      <c r="B43">
+        <v>7142999.7999999998</v>
       </c>
       <c r="C43" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
-      <c r="B44" t="n">
-        <v>5718064.48</v>
+      <c r="B44">
+        <v>5718064.4800000004</v>
       </c>
       <c r="C44" t="s">
         <v>4</v>
@@ -996,21 +1025,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1021,408 +1050,408 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1101809996.78</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>600241514.38</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="n">
-        <v>351990702.27</v>
+      <c r="B4">
+        <v>351990702.26999998</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="n">
-        <v>347406301.41</v>
+      <c r="B5">
+        <v>347406301.41000003</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>220744361.37</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>212822499.53</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="n">
-        <v>185045081.1</v>
+      <c r="B8">
+        <v>185045081.09999999</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="n">
-        <v>180826937.7</v>
+      <c r="B9">
+        <v>180826937.69999999</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
-      <c r="B10" t="n">
-        <v>170383392.46</v>
+      <c r="B10">
+        <v>170383392.46000001</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" t="n">
-        <v>136639445.6</v>
+      <c r="B11">
+        <v>136639445.59999999</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>126775323.52</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
-      <c r="B13" t="n">
-        <v>108588433.54</v>
+      <c r="B13">
+        <v>108588433.54000001</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="B14" t="n">
-        <v>99390405.57</v>
+      <c r="B14">
+        <v>99390405.569999993</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>10</v>
       </c>
-      <c r="B15" t="n">
-        <v>98158317.14</v>
+      <c r="B15">
+        <v>98158317.140000001</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
-      <c r="B16" t="n">
-        <v>93040490.04</v>
+      <c r="B16">
+        <v>93040490.040000007</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>34</v>
       </c>
-      <c r="B17" t="n">
-        <v>87069848.15</v>
+      <c r="B17">
+        <v>87069848.150000006</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
-      <c r="B18" t="n">
-        <v>81291999.61</v>
+      <c r="B18">
+        <v>81291999.609999999</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>29</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>74447548.75</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
-        <v>70724804.14</v>
+      <c r="B20">
+        <v>70724804.140000001</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B21" t="n">
-        <v>63267427.97</v>
+      <c r="B21">
+        <v>63267427.969999999</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>31</v>
       </c>
-      <c r="B22" t="n">
-        <v>62529149.79</v>
+      <c r="B22">
+        <v>62529149.789999999</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>39</v>
       </c>
-      <c r="B23" t="n">
-        <v>56657078.46</v>
+      <c r="B23">
+        <v>56657078.460000001</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>41</v>
       </c>
-      <c r="B24" t="n">
-        <v>54904383.22</v>
+      <c r="B24">
+        <v>54904383.219999999</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25" t="n">
-        <v>52270725.28</v>
+      <c r="B25">
+        <v>52270725.280000001</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>50060183.57</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B27" t="n">
-        <v>49864545.02</v>
+      <c r="B27">
+        <v>49864545.020000003</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>25</v>
       </c>
-      <c r="B28" t="n">
-        <v>44543882.09</v>
+      <c r="B28">
+        <v>44543882.090000004</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>43288844.75</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>44</v>
       </c>
-      <c r="B30" t="n">
-        <v>35219222.83</v>
+      <c r="B30">
+        <v>35219222.829999998</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>23</v>
       </c>
-      <c r="B31" t="n">
-        <v>30990805.4</v>
+      <c r="B31">
+        <v>30990805.399999999</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>25399363.48</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>15</v>
       </c>
-      <c r="B33" t="n">
-        <v>24533728.42</v>
+      <c r="B33">
+        <v>24533728.420000002</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>16</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>23977123.77</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>22644626.98</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
-      <c r="B36" t="n">
-        <v>18645420.61</v>
+      <c r="B36">
+        <v>18645420.609999999</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
-        <v>18356928.81</v>
+      <c r="B37">
+        <v>18356928.809999999</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38" t="n">
-        <v>14582661.61</v>
+      <c r="B38">
+        <v>14582661.609999999</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
@@ -1430,21 +1459,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1455,408 +1484,408 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1429672939.2</v>
       </c>
       <c r="C2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="n">
-        <v>746052295.93</v>
+      <c r="B3">
+        <v>746052295.92999995</v>
       </c>
       <c r="C3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="n">
-        <v>436852602.15</v>
+      <c r="B4">
+        <v>436852602.14999998</v>
       </c>
       <c r="C4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>35</v>
       </c>
-      <c r="B5" t="n">
-        <v>349073581.58</v>
+      <c r="B5">
+        <v>349073581.57999998</v>
       </c>
       <c r="C5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="n">
-        <v>332883795.39</v>
+      <c r="B6">
+        <v>332883795.38999999</v>
       </c>
       <c r="C6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="n">
-        <v>298461051.41</v>
+      <c r="B7">
+        <v>298461051.41000003</v>
       </c>
       <c r="C7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="n">
-        <v>296424561.18</v>
+      <c r="B8">
+        <v>296424561.18000001</v>
       </c>
       <c r="C8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
-      <c r="B9" t="n">
-        <v>247143435.68</v>
+      <c r="B9">
+        <v>247143435.68000001</v>
       </c>
       <c r="C9" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="n">
-        <v>206523028.55</v>
+      <c r="B10">
+        <v>206523028.55000001</v>
       </c>
       <c r="C10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
-      <c r="B11" t="n">
-        <v>197280762.21</v>
+      <c r="B11">
+        <v>197280762.21000001</v>
       </c>
       <c r="C11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>167964952.69</v>
       </c>
       <c r="C12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
-      <c r="B13" t="n">
-        <v>155658734.85</v>
+      <c r="B13">
+        <v>155658734.84999999</v>
       </c>
       <c r="C13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" t="n">
-        <v>153337952.05</v>
+      <c r="B14">
+        <v>153337952.05000001</v>
       </c>
       <c r="C14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
-        <v>151574936.85</v>
+      <c r="B15">
+        <v>151574936.84999999</v>
       </c>
       <c r="C15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
-      <c r="B16" t="n">
-        <v>146946999.79</v>
+      <c r="B16">
+        <v>146946999.78999999</v>
       </c>
       <c r="C16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>31</v>
       </c>
-      <c r="B17" t="n">
-        <v>142481479.77</v>
+      <c r="B17">
+        <v>142481479.77000001</v>
       </c>
       <c r="C17" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>103479165.03</v>
       </c>
       <c r="C18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
-      <c r="B19" t="n">
-        <v>102925321.93</v>
+      <c r="B19">
+        <v>102925321.93000001</v>
       </c>
       <c r="C19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>30</v>
       </c>
-      <c r="B20" t="n">
-        <v>93851867.98</v>
+      <c r="B20">
+        <v>93851867.980000004</v>
       </c>
       <c r="C20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>39</v>
       </c>
-      <c r="B21" t="n">
-        <v>93817428.26</v>
+      <c r="B21">
+        <v>93817428.260000005</v>
       </c>
       <c r="C21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>28</v>
       </c>
-      <c r="B22" t="n">
-        <v>89568767.49</v>
+      <c r="B22">
+        <v>89568767.489999995</v>
       </c>
       <c r="C22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>18</v>
       </c>
-      <c r="B23" t="n">
-        <v>82951894.61</v>
+      <c r="B23">
+        <v>82951894.609999999</v>
       </c>
       <c r="C23" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
-        <v>77742706.74</v>
+      <c r="B24">
+        <v>77742706.739999995</v>
       </c>
       <c r="C24" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
-      <c r="B25" t="n">
-        <v>71452837.21</v>
+      <c r="B25">
+        <v>71452837.209999993</v>
       </c>
       <c r="C25" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
-        <v>60530643.63</v>
+      <c r="B26">
+        <v>60530643.630000003</v>
       </c>
       <c r="C26" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>44</v>
       </c>
-      <c r="B27" t="n">
-        <v>57406570.56</v>
+      <c r="B27">
+        <v>57406570.560000002</v>
       </c>
       <c r="C27" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
-      <c r="B28" t="n">
-        <v>54011529.85</v>
+      <c r="B28">
+        <v>54011529.850000001</v>
       </c>
       <c r="C28" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>16</v>
       </c>
-      <c r="B29" t="n">
-        <v>50381442.36</v>
+      <c r="B29">
+        <v>50381442.359999999</v>
       </c>
       <c r="C29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>49643316.75</v>
       </c>
       <c r="C30" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>23</v>
       </c>
-      <c r="B31" t="n">
-        <v>41418364.97</v>
+      <c r="B31">
+        <v>41418364.969999999</v>
       </c>
       <c r="C31" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
-      <c r="B32" t="n">
-        <v>39870689.8</v>
+      <c r="B32">
+        <v>39870689.799999997</v>
       </c>
       <c r="C32" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
-      <c r="B33" t="n">
-        <v>38561759.2</v>
+      <c r="B33">
+        <v>38561759.200000003</v>
       </c>
       <c r="C33" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B34" t="n">
-        <v>31235629.03</v>
+      <c r="B34">
+        <v>31235629.030000001</v>
       </c>
       <c r="C34" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
-      <c r="B35" t="n">
-        <v>30242901.54</v>
+      <c r="B35">
+        <v>30242901.539999999</v>
       </c>
       <c r="C35" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>15</v>
       </c>
-      <c r="B36" t="n">
-        <v>25867593.51</v>
+      <c r="B36">
+        <v>25867593.510000002</v>
       </c>
       <c r="C36" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
-      <c r="B37" t="n">
-        <v>23596047.31</v>
+      <c r="B37">
+        <v>23596047.309999999</v>
       </c>
       <c r="C37" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38" t="n">
-        <v>7755286.35</v>
+      <c r="B38">
+        <v>7755286.3499999996</v>
       </c>
       <c r="C38" t="s">
         <v>48</v>
@@ -1864,21 +1893,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1889,407 +1918,407 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="n">
-        <v>1602939476.44</v>
+      <c r="B2">
+        <v>1602939476.4400001</v>
       </c>
       <c r="C2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="n">
-        <v>582641353.68</v>
+      <c r="B3">
+        <v>582641353.67999995</v>
       </c>
       <c r="C3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="n">
-        <v>336699262.54</v>
+      <c r="B4">
+        <v>336699262.54000002</v>
       </c>
       <c r="C4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="n">
-        <v>204758639.6</v>
+      <c r="B5">
+        <v>204758639.59999999</v>
       </c>
       <c r="C5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" t="n">
-        <v>198437703.51</v>
+      <c r="B6">
+        <v>198437703.50999999</v>
       </c>
       <c r="C6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>180481051.88</v>
       </c>
       <c r="C7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>31</v>
       </c>
-      <c r="B8" t="n">
-        <v>173955689.05</v>
+      <c r="B8">
+        <v>173955689.05000001</v>
       </c>
       <c r="C8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>168677511.72</v>
       </c>
       <c r="C9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
-        <v>167217155.17</v>
+      <c r="B10">
+        <v>167217155.16999999</v>
       </c>
       <c r="C10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" t="n">
-        <v>165788597.73</v>
+      <c r="B11">
+        <v>165788597.72999999</v>
       </c>
       <c r="C11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>41</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>161763597.72</v>
       </c>
       <c r="C12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
-      <c r="B13" t="n">
-        <v>161650429.46</v>
+      <c r="B13">
+        <v>161650429.46000001</v>
       </c>
       <c r="C13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" t="n">
-        <v>136831474.89</v>
+      <c r="B14">
+        <v>136831474.88999999</v>
       </c>
       <c r="C14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>10</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>117204155.13</v>
       </c>
       <c r="C15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>39</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>105893712.17</v>
       </c>
       <c r="C16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>102049762.94</v>
       </c>
       <c r="C17" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" t="n">
-        <v>96724806.43</v>
+      <c r="B18">
+        <v>96724806.430000007</v>
       </c>
       <c r="C18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
-      <c r="B19" t="n">
-        <v>91594945.72</v>
+      <c r="B19">
+        <v>91594945.719999999</v>
       </c>
       <c r="C19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
-      <c r="B20" t="n">
-        <v>84333994.94</v>
+      <c r="B20">
+        <v>84333994.939999998</v>
       </c>
       <c r="C20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>30</v>
       </c>
-      <c r="B21" t="n">
-        <v>79740030.13</v>
+      <c r="B21">
+        <v>79740030.129999995</v>
       </c>
       <c r="C21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
-      <c r="B22" t="n">
-        <v>77708608.54</v>
+      <c r="B22">
+        <v>77708608.540000007</v>
       </c>
       <c r="C22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
-      <c r="B23" t="n">
-        <v>70721904.05</v>
+      <c r="B23">
+        <v>70721904.049999997</v>
       </c>
       <c r="C23" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
-      <c r="B24" t="n">
-        <v>70635388.02</v>
+      <c r="B24">
+        <v>70635388.019999996</v>
       </c>
       <c r="C24" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B25" t="n">
-        <v>70022022.54</v>
+      <c r="B25">
+        <v>70022022.540000007</v>
       </c>
       <c r="C25" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>65629884.82</v>
       </c>
       <c r="C26" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>22</v>
       </c>
-      <c r="B27" t="n">
-        <v>64235705.92</v>
+      <c r="B27">
+        <v>64235705.920000002</v>
       </c>
       <c r="C27" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>17</v>
       </c>
-      <c r="B28" t="n">
-        <v>64191220.03</v>
+      <c r="B28">
+        <v>64191220.030000001</v>
       </c>
       <c r="C28" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>3</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>58515300</v>
       </c>
       <c r="C29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>34</v>
       </c>
-      <c r="B30" t="n">
-        <v>48676742.54</v>
+      <c r="B30">
+        <v>48676742.539999999</v>
       </c>
       <c r="C30" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>15</v>
       </c>
-      <c r="B31" t="n">
-        <v>34040564.92</v>
+      <c r="B31">
+        <v>34040564.920000002</v>
       </c>
       <c r="C31" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
-      <c r="B32" t="n">
-        <v>30436283.97</v>
+      <c r="B32">
+        <v>30436283.969999999</v>
       </c>
       <c r="C32" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>37</v>
       </c>
-      <c r="B33" t="n">
-        <v>27409820.53</v>
+      <c r="B33">
+        <v>27409820.530000001</v>
       </c>
       <c r="C33" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>22743229.52</v>
       </c>
       <c r="C34" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>32</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>16841500</v>
       </c>
       <c r="C35" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>36</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>10479200</v>
       </c>
       <c r="C36" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>7790380</v>
       </c>
       <c r="C37" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>869000</v>
       </c>
       <c r="C38" t="s">
@@ -2298,21 +2327,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:C44"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2323,474 +2352,474 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="n">
-        <v>19036776760.85</v>
+      <c r="B2" s="2">
+        <v>19036776760.849998</v>
       </c>
       <c r="C2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="n">
-        <v>7944321077.89</v>
+      <c r="B3" s="2">
+        <v>7944321077.8900003</v>
       </c>
       <c r="C3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="n">
-        <v>7359873737.8</v>
+      <c r="B4" s="2">
+        <v>7359873737.8000002</v>
       </c>
       <c r="C4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="n">
-        <v>6400159851.61</v>
+      <c r="B5" s="2">
+        <v>6400159851.6099997</v>
       </c>
       <c r="C5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" t="n">
-        <v>6037527845.65</v>
+      <c r="B6" s="2">
+        <v>6037527845.6499996</v>
       </c>
       <c r="C6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="2">
         <v>5900118576.71</v>
       </c>
       <c r="C7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="2">
         <v>5398461292.25</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="n">
-        <v>5100710343.76</v>
+      <c r="B9" s="2">
+        <v>5100710343.7600002</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
-      <c r="B10" t="n">
-        <v>5080663436.93</v>
+      <c r="B10" s="2">
+        <v>5080663436.9300003</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
-      <c r="B11" t="n">
-        <v>4902924662.9</v>
+      <c r="B11" s="2">
+        <v>4902924662.8999996</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>44</v>
       </c>
-      <c r="B12" t="n">
-        <v>4796707316.34</v>
+      <c r="B12" s="2">
+        <v>4796707316.3400002</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="n">
-        <v>4483245355.48</v>
+      <c r="B13" s="2">
+        <v>4483245355.4799995</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="2">
         <v>4458864057.96</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
-      <c r="B15" t="n">
-        <v>4438163027.12</v>
+      <c r="B15" s="2">
+        <v>4438163027.1199999</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>8</v>
       </c>
-      <c r="B16" t="n">
-        <v>4433378806.81</v>
+      <c r="B16" s="2">
+        <v>4433378806.8100004</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
-      <c r="B17" t="n">
-        <v>4250282101.89</v>
+      <c r="B17" s="2">
+        <v>4250282101.8899999</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" t="n">
-        <v>4243871989.41</v>
+      <c r="B18" s="2">
+        <v>4243871989.4099998</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
-      <c r="B19" t="n">
-        <v>4019744320.74</v>
+      <c r="B19" s="2">
+        <v>4019744320.7399998</v>
       </c>
       <c r="C19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="2">
         <v>3622379109.21</v>
       </c>
       <c r="C20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
-      <c r="B21" t="n">
-        <v>3513433251.99</v>
+      <c r="B21" s="2">
+        <v>3513433251.9899998</v>
       </c>
       <c r="C21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="B22" t="n">
-        <v>3409640138.38</v>
+      <c r="B22" s="2">
+        <v>3409640138.3800001</v>
       </c>
       <c r="C22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23" t="n">
-        <v>3231155181.28</v>
+      <c r="B23" s="2">
+        <v>3231155181.2800002</v>
       </c>
       <c r="C23" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>34</v>
       </c>
-      <c r="B24" t="n">
-        <v>3209811928.42</v>
+      <c r="B24" s="2">
+        <v>3209811928.4200001</v>
       </c>
       <c r="C24" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
-      <c r="B25" t="n">
-        <v>3102952241.87</v>
+      <c r="B25" s="2">
+        <v>3102952241.8699999</v>
       </c>
       <c r="C25" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>10</v>
       </c>
-      <c r="B26" t="n">
-        <v>3038775221.87</v>
+      <c r="B26" s="2">
+        <v>3038775221.8699999</v>
       </c>
       <c r="C26" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>41</v>
       </c>
-      <c r="B27" t="n">
-        <v>2994288449.45</v>
+      <c r="B27" s="2">
+        <v>2994288449.4499998</v>
       </c>
       <c r="C27" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>16</v>
       </c>
-      <c r="B28" t="n">
-        <v>2852200077.17</v>
+      <c r="B28" s="2">
+        <v>2852200077.1700001</v>
       </c>
       <c r="C28" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
-      <c r="B29" t="n">
-        <v>2731552582.97</v>
+      <c r="B29" s="2">
+        <v>2731552582.9699998</v>
       </c>
       <c r="C29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>27</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="2">
         <v>2581312663.25</v>
       </c>
       <c r="C30" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="2">
         <v>2468628760.5</v>
       </c>
       <c r="C31" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
-      <c r="B32" t="n">
-        <v>2360697353.65</v>
+      <c r="B32" s="2">
+        <v>2360697353.6500001</v>
       </c>
       <c r="C32" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="B33" t="n">
-        <v>2247810930.84</v>
+      <c r="B33" s="2">
+        <v>2247810930.8400002</v>
       </c>
       <c r="C33" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
-      <c r="B34" t="n">
-        <v>1947080343.39</v>
+      <c r="B34" s="2">
+        <v>1947080343.3900001</v>
       </c>
       <c r="C34" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>26</v>
       </c>
-      <c r="B35" t="n">
-        <v>1873583999.14</v>
+      <c r="B35" s="2">
+        <v>1873583999.1400001</v>
       </c>
       <c r="C35" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>43</v>
       </c>
-      <c r="B36" t="n">
-        <v>1630002860.81</v>
+      <c r="B36" s="2">
+        <v>1630002860.8099999</v>
       </c>
       <c r="C36" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>40</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="2">
         <v>1374859978.54</v>
       </c>
       <c r="C37" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>3</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="2">
         <v>1324739542.46</v>
       </c>
       <c r="C38" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
-      <c r="B39" t="n">
-        <v>841761096.64</v>
+      <c r="B39" s="2">
+        <v>841761096.63999999</v>
       </c>
       <c r="C39" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>45</v>
       </c>
-      <c r="B40" t="n">
-        <v>592531970.11</v>
+      <c r="B40" s="2">
+        <v>592531970.11000001</v>
       </c>
       <c r="C40" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>32</v>
       </c>
-      <c r="B41" t="n">
-        <v>577883219.36</v>
+      <c r="B41" s="2">
+        <v>577883219.36000001</v>
       </c>
       <c r="C41" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>42</v>
       </c>
-      <c r="B42" t="n">
-        <v>405136298.6</v>
+      <c r="B42" s="2">
+        <v>405136298.60000002</v>
       </c>
       <c r="C42" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>36</v>
       </c>
-      <c r="B43" t="n">
-        <v>296133977.71</v>
+      <c r="B43" s="2">
+        <v>296133977.70999998</v>
       </c>
       <c r="C43" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
-      <c r="B44" t="n">
-        <v>198230875.08</v>
+      <c r="B44" s="2">
+        <v>198230875.08000001</v>
       </c>
       <c r="C44" t="s">
         <v>48</v>
@@ -2798,6 +2827,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{f398df9c-fd0c-4829-a003-c770a1c4a063}" enabled="0" method="" siteId="{f398df9c-fd0c-4829-a003-c770a1c4a063}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/R Markdown/resultados/Produtos_Cesta_2026/tabelas/tabela_valores_por_subprefeitura.xlsx
+++ b/R Markdown/resultados/Produtos_Cesta_2026/tabelas/tabela_valores_por_subprefeitura.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/resultados/Produtos_Cesta_2026/tabelas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_05881C1CD90F55B416BB1BBBCC2088D9147CA8D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F0EB0B8-B0ED-457C-95F7-AE6FD6BE3642}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_05881C1CD90F55B416BB1BBBCC2088D9147CA8D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E1FFF6F-62E8-424C-94E8-65C52EAEEC44}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2022" sheetId="1" r:id="rId1"/>
@@ -202,7 +202,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,6 +212,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1A1442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -228,12 +234,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1469,7 +1477,7 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="65.85546875" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2716,112 +2724,112 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="4">
         <v>1873583999.1400001</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="4">
         <v>1630002860.8099999</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="4">
         <v>1374859978.54</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="4">
         <v>1324739542.46</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="4">
         <v>841761096.63999999</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="4">
         <v>592531970.11000001</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="4">
         <v>577883219.36000001</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="4">
         <v>405136298.60000002</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="4">
         <v>296133977.70999998</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="4">
         <v>198230875.08000001</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="3" t="s">
         <v>48</v>
       </c>
     </row>

--- a/R Markdown/resultados/Produtos_Cesta_2026/tabelas/tabela_valores_por_subprefeitura.xlsx
+++ b/R Markdown/resultados/Produtos_Cesta_2026/tabelas/tabela_valores_por_subprefeitura.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30121"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="5" documentId="11_05881C1CD90F55B416BB1BBBCC2088D9147CA8D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E1FFF6F-62E8-424C-94E8-65C52EAEEC44}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2022" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,23 @@
     <sheet name="2025" sheetId="4" r:id="rId4"/>
     <sheet name="Agregado_2022_2025" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -180,7 +196,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -540,14 +556,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -569,7 +585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -580,7 +596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -591,7 +607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -602,7 +618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -613,7 +629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -624,7 +640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -635,7 +651,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -646,7 +662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -657,7 +673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -668,7 +684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -679,7 +695,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -690,7 +706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -701,7 +717,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -712,7 +728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -723,7 +739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -734,7 +750,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -745,7 +761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -756,7 +772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -767,7 +783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -778,7 +794,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -789,7 +805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -800,7 +816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -811,7 +827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -822,7 +838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -833,7 +849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -844,7 +860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -855,7 +871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -866,7 +882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -877,7 +893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -888,7 +904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -899,7 +915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -910,7 +926,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -921,7 +937,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -932,7 +948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -943,7 +959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -954,7 +970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -965,7 +981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -976,7 +992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -987,7 +1003,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -998,7 +1014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1009,7 +1025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1020,7 +1036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -1040,14 +1056,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C38"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1058,7 +1074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1069,7 +1085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1080,7 +1096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1091,7 +1107,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1102,7 +1118,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1113,7 +1129,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1124,7 +1140,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1135,7 +1151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1146,7 +1162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1157,7 +1173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1168,7 +1184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1179,7 +1195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1190,7 +1206,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1201,7 +1217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1212,7 +1228,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1223,7 +1239,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1234,7 +1250,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1245,7 +1261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1256,7 +1272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1267,7 +1283,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1278,7 +1294,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -1289,7 +1305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -1300,7 +1316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -1311,7 +1327,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -1322,7 +1338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -1333,7 +1349,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1344,7 +1360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -1355,7 +1371,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1366,7 +1382,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -1377,7 +1393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -1388,7 +1404,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -1399,7 +1415,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -1410,7 +1426,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -1421,7 +1437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1432,7 +1448,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1443,7 +1459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -1454,7 +1470,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -1474,14 +1490,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C38"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
     <col min="2" max="2" width="65.85546875" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1492,7 +1508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1503,7 +1519,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1514,7 +1530,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1525,7 +1541,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -1536,7 +1552,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1547,7 +1563,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1558,7 +1574,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1569,7 +1585,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -1580,7 +1596,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1591,7 +1607,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1602,7 +1618,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1613,7 +1629,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -1624,7 +1640,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1635,7 +1651,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1646,7 +1662,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1657,7 +1673,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -1668,7 +1684,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1679,7 +1695,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -1690,7 +1706,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -1701,7 +1717,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -1712,7 +1728,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -1723,7 +1739,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -1734,7 +1750,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -1745,7 +1761,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1756,7 +1772,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1767,7 +1783,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>44</v>
       </c>
@@ -1778,7 +1794,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1789,7 +1805,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -1800,7 +1816,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -1811,7 +1827,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -1822,7 +1838,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -1833,7 +1849,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1844,7 +1860,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -1855,7 +1871,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1866,7 +1882,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -1877,7 +1893,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -1888,7 +1904,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -1908,14 +1924,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C38"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
     <col min="2" max="2" width="29.140625" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1926,7 +1942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1937,7 +1953,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1948,7 +1964,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1959,7 +1975,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1970,7 +1986,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1981,7 +1997,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1992,7 +2008,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -2003,7 +2019,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2014,7 +2030,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2025,7 +2041,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2036,7 +2052,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -2047,7 +2063,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2058,7 +2074,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -2069,7 +2085,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -2080,7 +2096,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -2091,7 +2107,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -2102,7 +2118,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2113,7 +2129,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -2124,7 +2140,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -2135,7 +2151,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -2146,7 +2162,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2157,7 +2173,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -2168,7 +2184,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -2179,7 +2195,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2190,7 +2206,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -2201,7 +2217,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -2212,7 +2228,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -2223,7 +2239,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -2234,7 +2250,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -2245,7 +2261,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -2256,7 +2272,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2267,7 +2283,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -2278,7 +2294,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -2289,7 +2305,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -2300,7 +2316,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -2311,7 +2327,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -2322,7 +2338,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -2342,14 +2358,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
     <col min="2" max="2" width="35.140625" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2360,7 +2376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2371,7 +2387,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2382,7 +2398,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -2393,7 +2409,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2404,7 +2420,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -2415,7 +2431,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -2426,7 +2442,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2437,7 +2453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -2448,7 +2464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -2459,7 +2475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2470,7 +2486,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -2481,7 +2497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -2492,7 +2508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -2503,7 +2519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -2514,7 +2530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -2525,7 +2541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -2536,7 +2552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2547,7 +2563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -2558,7 +2574,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2569,7 +2585,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2580,7 +2596,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -2591,7 +2607,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2602,7 +2618,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -2613,7 +2629,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -2624,7 +2640,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -2635,7 +2651,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>41</v>
       </c>
@@ -2646,7 +2662,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -2657,7 +2673,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -2668,7 +2684,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -2679,7 +2695,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -2690,7 +2706,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -2701,7 +2717,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -2712,7 +2728,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -2723,7 +2739,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" s="3" t="s">
         <v>26</v>
       </c>
@@ -2734,7 +2750,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" s="3" t="s">
         <v>43</v>
       </c>
@@ -2745,7 +2761,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
         <v>40</v>
       </c>
@@ -2756,7 +2772,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" s="3" t="s">
         <v>3</v>
       </c>
@@ -2767,7 +2783,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" s="3" t="s">
         <v>38</v>
       </c>
@@ -2778,7 +2794,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" s="3" t="s">
         <v>45</v>
       </c>
@@ -2789,7 +2805,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" s="3" t="s">
         <v>32</v>
       </c>
@@ -2800,7 +2816,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
@@ -2811,7 +2827,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43" s="3" t="s">
         <v>36</v>
       </c>
@@ -2822,7 +2838,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
